--- a/registration_forms/043_freelancer_growth_bundle_registration--registration_forms.xlsx
+++ b/registration_forms/043_freelancer_growth_bundle_registration--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>notes_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>notes_3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>experience_levels</t>
+          <t>experience_levels_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Experience Levels</t>
+          <t>Experience Levels 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,7 +773,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>notes_4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>email_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>phone_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>coach</t>
+          <t>coach_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Coach</t>
+          <t>Coach 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>coach</t>
+          <t>coach_3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Coach</t>
+          <t>Coach 3</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>coach</t>
+          <t>coach_4</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Coach</t>
+          <t>Coach 4</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>coach</t>
+          <t>coach_5</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Coach</t>
+          <t>Coach 5</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -983,11 +983,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -1016,12 +1016,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1033,12 +1033,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1050,12 +1050,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1135,12 +1135,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1152,29 +1152,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>program_owner_choices</t>
+          <t>organize_applicants_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1186,46 +1186,46 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>coach_choices</t>
+          <t>program_owner_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>coach_choices</t>
+          <t>program_owner_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1271,95 +1271,163 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>coach_choices</t>
+          <t>coach_2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>coach_choices</t>
+          <t>coach_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>coach_choices</t>
+          <t>coach_3_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>coach_choices</t>
+          <t>coach_3_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>coach_choices</t>
+          <t>coach_3_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>coach_4_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>coach_4_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>coach_5_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>coach_5_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
         <is>
           <t>No</t>
         </is>
